--- a/workbook/amazon-de-seller-workbook-v4-EN.xlsx
+++ b/workbook/amazon-de-seller-workbook-v4-EN.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C12" authorId="0">
@@ -81,7 +81,7 @@
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="M5" authorId="0">
@@ -103,7 +103,7 @@
 <file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C5" authorId="0">
@@ -125,7 +125,7 @@
 <file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C20" authorId="0">
@@ -147,7 +147,7 @@
 <file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C8" authorId="0">
@@ -181,7 +181,7 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C29" authorId="0">
@@ -227,7 +227,7 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C18" authorId="0">
@@ -261,7 +261,7 @@
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C43" authorId="0">
@@ -283,7 +283,7 @@
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C21" authorId="0">
@@ -317,7 +317,7 @@
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>Unknown Author</author>
+    <author>Workbook</author>
   </authors>
   <commentList>
     <comment ref="C8" authorId="0">
@@ -1323,10 +1323,10 @@
     <t xml:space="preserve">P10/P90 helper — from Cerebro keyword sales (v4)</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyword sales per month (Cerebro, niche keywords summed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerebro column 'Keyword Sales' = purchases attributed to the keyword(s). Sum the parent + main children, don't double-count overlapping terms.</t>
+    <t xml:space="preserve">Keyword sales per WEEK (Cerebro, niche keywords summed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerebro column 'Keyword Sales' = purchases attributed to the keyword(s), counted PER WEEK (hover the column header in Cerebro - it says weekly). Rows 40/41 convert to months with x52/12. Earlier versions of this sheet read this figure as monthly, which made every suggested order about 4.3x too small. Sum the parent + main children, don't double-count overlapping terms.</t>
   </si>
   <si>
     <t xml:space="preserve">Months you are buying stock for</t>
@@ -1861,18 +1861,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00&quot; €&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="0%"/>
-    <numFmt numFmtId="174" formatCode="\Q0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.00&quot; €&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="173" formatCode="\Q0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2072,7 +2071,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2088,7 +2087,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2096,11 +2095,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2108,11 +2107,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2124,23 +2131,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2148,11 +2147,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2236,34 +2235,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2410,7 +2409,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
@@ -2498,7 +2497,7 @@
       </c>
       <c r="E11" s="7" t="str">
         <f aca="false">IFERROR("order by "&amp;TEXT('2 Order timing'!C20,"yyyy-mm-dd")&amp;" · "&amp;TEXT('2 Order timing'!C21,"0")&amp;" days left","fill Sheet 2")</f>
-        <v>order by 2026-10-24 · 60 days left</v>
+        <v>order by 2026-10-24 · 56 days left</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2694,7 +2693,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:I38"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
@@ -3247,7 +3246,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:M21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="8"/>
@@ -3777,7 +3776,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:F136"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -4758,7 +4757,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:D33"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
@@ -5025,7 +5024,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:N38"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
@@ -5824,7 +5823,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:B33"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
@@ -5959,7 +5958,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:I38"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
@@ -6530,7 +6529,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:E23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
@@ -6704,7 +6703,7 @@
       </c>
       <c r="C21" s="23" t="n">
         <f aca="true">C7-C18-TODAY()</f>
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6730,7 +6729,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:E36"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
@@ -7071,7 +7070,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:E46"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
@@ -7464,7 +7463,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:K37"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
@@ -8316,7 +8315,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:E43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
@@ -8577,12 +8576,12 @@
       </c>
       <c r="C35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="11" t="s">
         <v>324</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>325</v>
@@ -8617,8 +8616,8 @@
         <v>329</v>
       </c>
       <c r="C40" s="13" t="n">
-        <f aca="false">IFERROR(ROUND(C36*C38*C37,0),"")</f>
-        <v>91</v>
+        <f aca="false">IFERROR(ROUND(C36*(52/12)*C38*C37,0),"")</f>
+        <v>92</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8626,8 +8625,8 @@
         <v>330</v>
       </c>
       <c r="C41" s="13" t="n">
-        <f aca="false">IFERROR(ROUND(C36*C39*C37,0),"")</f>
-        <v>342</v>
+        <f aca="false">IFERROR(ROUND(C36*(52/12)*C39*C37,0),"")</f>
+        <v>343</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8654,7 +8653,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:J229"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
